--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F93D96-3462-4580-B84B-6790FD6D1CD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FB353EB8DFAB3EDAA6B391E871D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72871791-1DB7-4D2C-A1F7-7293866D7D6F}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 14-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -650,9 +650,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -786,7 +786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -824,7 +824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -858,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -931,7 +931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -989,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>93</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FB353EB8DFAB3EDAA6B391E871D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72871791-1DB7-4D2C-A1F7-7293866D7D6F}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FB353EB8DFAB3EE86EF7B39A70D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C740D6-5BA4-470B-93A8-BFD58A62D586}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9FB353EB8DFAB3EE86EF7B39A70D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C740D6-5BA4-470B-93A8-BFD58A62D586}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63D1389-0FED-4C64-BCD8-3C883DC06CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
@@ -650,9 +650,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -786,7 +786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -824,7 +824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -858,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -931,7 +931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -989,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>93</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Godkendelsesdatabase\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D63D1389-0FED-4C64-BCD8-3C883DC06CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4304B1AF-FA69-42D2-948D-B0550BDF4FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1440" yWindow="1632" windowWidth="21600" windowHeight="11232" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 14-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 14-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 17-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -58,7 +58,7 @@
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (Xmedicus Systems)</t>
+    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -650,9 +650,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -786,7 +786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -824,7 +824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -858,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -931,7 +931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -989,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4304B1AF-FA69-42D2-948D-B0550BDF4FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9413A154-070C-45F6-A818-352A166AE1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9413A154-070C-45F6-A818-352A166AE1B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D9853CA581AA3E76DEB5826670D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C2FB315-70F2-4B7B-8C64-53DADFC86EB0}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 17-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 17-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 18-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -650,9 +650,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -786,7 +786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -824,7 +824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -858,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -931,7 +931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -989,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>93</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D9853CA581AA3E76DEB5826670D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C2FB315-70F2-4B7B-8C64-53DADFC86EB0}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D9853CA581AA3E9E263696D871D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50347547-6DCC-4D00-8F76-838AFDCBB140}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 18-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 18-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 21-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9D9853CA581AA3E9E263696D871D84C34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{50347547-6DCC-4D00-8F76-838AFDCBB140}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D83B35E-1061-4BC7-B401-D93A186A635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
@@ -650,9 +650,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -693,7 +693,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -713,7 +713,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -748,7 +748,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -786,7 +786,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -824,7 +824,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>25</v>
       </c>
@@ -835,7 +835,7 @@
         <v>15</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
         <v>17</v>
@@ -844,7 +844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>27</v>
       </c>
@@ -858,7 +858,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>27</v>
       </c>
@@ -890,7 +890,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>30</v>
       </c>
@@ -931,7 +931,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -972,7 +972,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>34</v>
       </c>
@@ -989,7 +989,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>36</v>
       </c>
@@ -1006,7 +1006,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1020,7 +1020,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -1049,7 +1049,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>42</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>44</v>
       </c>
@@ -1104,7 +1104,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>46</v>
       </c>
@@ -1121,7 +1121,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>48</v>
       </c>
@@ -1144,7 +1144,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>50</v>
       </c>
@@ -1182,7 +1182,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1220,7 +1220,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>54</v>
       </c>
@@ -1261,7 +1261,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>56</v>
       </c>
@@ -1302,7 +1302,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>58</v>
       </c>
@@ -1337,7 +1337,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>58</v>
       </c>
@@ -1375,7 +1375,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>61</v>
       </c>
@@ -1413,7 +1413,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>63</v>
       </c>
@@ -1451,7 +1451,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>65</v>
       </c>
@@ -1489,7 +1489,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>67</v>
       </c>
@@ -1527,7 +1527,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>71</v>
       </c>
@@ -1594,7 +1594,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>73</v>
       </c>
@@ -1611,7 +1611,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>75</v>
       </c>
@@ -1634,7 +1634,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>75</v>
       </c>
@@ -1648,7 +1648,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>78</v>
       </c>
@@ -1662,7 +1662,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>78</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>81</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>83</v>
       </c>
@@ -1704,7 +1704,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>85</v>
       </c>
@@ -1736,7 +1736,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>87</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>89</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>91</v>
       </c>
@@ -1820,7 +1820,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>93</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D83B35E-1061-4BC7-B401-D93A186A635E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A259AC4-5A06-4979-B58B-0795AAB0B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 21-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 21-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$M$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A259AC4-5A06-4979-B58B-0795AAB0B5AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA1BBB-4E3F-4E68-B7ED-B0805D840E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA1BBB-4E3F-4E68-B7ED-B0805D840E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA3B6BC-A750-4930-AD03-1DEE427EF0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 23-09-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t>Novax _LPS_ (Novax)</t>
+  </si>
+  <si>
+    <t>PraksisJournal (PraksisJournal)</t>
   </si>
   <si>
     <t>Vena (Vena)</t>
@@ -649,10 +652,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -692,1170 +695,1179 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>59</v>
       </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" t="s">
-        <v>16</v>
-      </c>
-      <c r="L23" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
-      </c>
-      <c r="J29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>75</v>
-      </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
-      </c>
-      <c r="J35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA3B6BC-A750-4930-AD03-1DEE427EF0B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB981FD31F1FFC92D84EEB6B7BC70D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1702781E-B7E3-40A3-8E7D-4FD3D8D941F9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -757,7 +757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -795,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -833,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -856,7 +856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -943,7 +943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -984,7 +984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1623,7 +1623,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1646,7 +1646,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1660,7 +1660,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1688,7 +1688,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1702,7 +1702,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1716,7 +1716,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1780,7 +1780,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1794,7 +1794,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1832,7 +1832,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB981FD31F1FFC92D84EEB6B7BC70D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1702781E-B7E3-40A3-8E7D-4FD3D8D941F9}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9058DB7E33FC92D579EB2A3E471D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E049B1-12B4-45E6-81B6-F25EB2A57CE2}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 23-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 23-09-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 24-09-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -61,7 +61,7 @@
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
+    <t>XMedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -91,7 +91,7 @@
     <t>Ikke Godkendt</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9058DB7E33FC92D579EB2A3E471D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E4E049B1-12B4-45E6-81B6-F25EB2A57CE2}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9058DB7E33FC92DBF36F485C071D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19FDF2B-85C3-4F5F-834F-F766944B2BC9}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,25 +5,25 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9058DB7E33FC92DBF36F485C071D84DEB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E19FDF2B-85C3-4F5F-834F-F766944B2BC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE54D34-3864-4974-8B9A-E6A11935BF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 24-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 24-09-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 28-09-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="377" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -757,7 +757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -795,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -833,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -856,7 +856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -943,7 +943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -984,7 +984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1232,7 +1232,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1314,7 +1314,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1387,7 +1387,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1425,7 +1425,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1501,7 +1501,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1606,7 +1606,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1622,8 +1622,11 @@
       <c r="L31" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1660,7 +1663,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1674,7 +1677,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1702,7 +1705,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1780,7 +1783,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1794,7 +1797,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1832,7 +1835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BE54D34-3864-4974-8B9A-E6A11935BF2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9194DB5CF8DC92D76EE349B7871D84ECF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAA33EBF-9514-4CE7-BD66-F8199C612438}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="5410" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 28-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 28-09-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 02-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -757,7 +757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -795,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -833,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -856,7 +856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -943,7 +943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -984,7 +984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1222,6 +1222,9 @@
       <c r="I20" t="s">
         <v>17</v>
       </c>
+      <c r="J20" t="s">
+        <v>18</v>
+      </c>
       <c r="K20" t="s">
         <v>17</v>
       </c>
@@ -1232,7 +1235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1273,7 +1276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1314,7 +1317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1349,7 +1352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1387,7 +1390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1425,7 +1428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1463,7 +1466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1501,7 +1504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1539,7 +1542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1564,6 +1567,9 @@
       <c r="I29" t="s">
         <v>17</v>
       </c>
+      <c r="J29" t="s">
+        <v>18</v>
+      </c>
       <c r="K29" t="s">
         <v>17</v>
       </c>
@@ -1574,7 +1580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1606,7 +1612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1626,7 +1632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1649,7 +1655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1663,7 +1669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1677,7 +1683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1687,11 +1693,14 @@
       <c r="C35" t="s">
         <v>16</v>
       </c>
+      <c r="J35" t="s">
+        <v>18</v>
+      </c>
       <c r="K35" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1705,7 +1714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1719,7 +1728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1751,7 +1760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1783,7 +1792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1797,7 +1806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1835,7 +1844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -1,29 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5BA1BBB-4E3F-4E68-B7ED-B0805D840E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989BC950-828C-4B6D-A156-8395C1579728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 22-09-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 22-09-2026'!$A$1:$M$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="374" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="96">
   <si>
     <t>Standard</t>
   </si>
@@ -52,13 +52,16 @@
     <t>Novax _LPS_ (Novax)</t>
   </si>
   <si>
+    <t>PraksisJournal (PraksisJournal)</t>
+  </si>
+  <si>
     <t>Vena (Vena)</t>
   </si>
   <si>
     <t>WinPLC _LPS_ (EG)</t>
   </si>
   <si>
-    <t>Xmedicus _LPS_ (XMedicus Systems)</t>
+    <t>XMedicus _LPS_ (XMedicus Systems)</t>
   </si>
   <si>
     <t>XMO _LPS_ (CGM)</t>
@@ -88,7 +91,7 @@
     <t>Ikke Godkendt</t>
   </si>
   <si>
-    <t>Binær dokumenttransport</t>
+    <t>Binær Dokumenttransport</t>
   </si>
   <si>
     <t>BIN01 (B0131X)</t>
@@ -649,10 +652,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:N42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -692,1170 +695,1191 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="K3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" t="s">
         <v>21</v>
       </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>20</v>
-      </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" t="s">
-        <v>16</v>
-      </c>
-      <c r="J4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M4" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L4" t="s">
+        <v>17</v>
+      </c>
+      <c r="N4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" t="s">
-        <v>16</v>
-      </c>
-      <c r="J5" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" t="s">
-        <v>16</v>
-      </c>
-      <c r="M5" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="N5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="N7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>28</v>
       </c>
-      <c r="C7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>27</v>
-      </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I8" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K8" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L8" t="s">
+        <v>17</v>
+      </c>
+      <c r="N8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I9" t="s">
-        <v>16</v>
-      </c>
-      <c r="J9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L9" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M9" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M10" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L11" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C12" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="M12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s">
-        <v>16</v>
-      </c>
-      <c r="K14" t="s">
-        <v>16</v>
-      </c>
-      <c r="M14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L14" t="s">
+        <v>17</v>
+      </c>
+      <c r="N14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I15" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F16" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" t="s">
-        <v>16</v>
-      </c>
-      <c r="K16" t="s">
-        <v>16</v>
-      </c>
-      <c r="M16" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L16" t="s">
+        <v>17</v>
+      </c>
+      <c r="N16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C17" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G18" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I18" t="s">
-        <v>16</v>
-      </c>
-      <c r="J18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="K18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I19" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M19" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C20" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J20" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" t="s">
-        <v>16</v>
-      </c>
-      <c r="M20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L20" t="s">
+        <v>17</v>
+      </c>
+      <c r="N20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C21" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I21" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M21" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E22" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F22" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I22" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M22" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C23" t="s">
+        <v>16</v>
+      </c>
+      <c r="D23" t="s">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="L23" t="s">
+        <v>17</v>
+      </c>
+      <c r="M23" t="s">
+        <v>17</v>
+      </c>
+      <c r="N23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>59</v>
       </c>
-      <c r="C23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F23" t="s">
-        <v>17</v>
-      </c>
-      <c r="G23" t="s">
-        <v>16</v>
-      </c>
-      <c r="H23" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" t="s">
-        <v>16</v>
-      </c>
-      <c r="L23" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>58</v>
-      </c>
       <c r="B24" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C24" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I24" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K24" t="s">
-        <v>16</v>
-      </c>
-      <c r="M24" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L24" t="s">
+        <v>17</v>
+      </c>
+      <c r="N24" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B25" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C25" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E25" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I25" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K25" t="s">
-        <v>16</v>
-      </c>
-      <c r="M25" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L25" t="s">
+        <v>17</v>
+      </c>
+      <c r="N25" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C26" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F26" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
-      </c>
-      <c r="J26" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M26" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L26" t="s">
+        <v>17</v>
+      </c>
+      <c r="N26" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B27" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C27" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F27" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I27" t="s">
-        <v>16</v>
-      </c>
-      <c r="J27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" t="s">
-        <v>16</v>
-      </c>
-      <c r="M27" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L27" t="s">
+        <v>17</v>
+      </c>
+      <c r="N27" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B28" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C28" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E28" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F28" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I28" t="s">
-        <v>16</v>
-      </c>
-      <c r="J28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K28" t="s">
-        <v>16</v>
-      </c>
-      <c r="M28" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L28" t="s">
+        <v>17</v>
+      </c>
+      <c r="N28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B29" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C29" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E29" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J29" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K29" t="s">
-        <v>16</v>
-      </c>
-      <c r="M29" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L29" t="s">
+        <v>17</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B30" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C30" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I30" t="s">
-        <v>16</v>
-      </c>
-      <c r="K30" t="s">
-        <v>16</v>
-      </c>
-      <c r="M30" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L30" t="s">
+        <v>17</v>
+      </c>
+      <c r="N30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B31" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C31" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I31" t="s">
-        <v>17</v>
-      </c>
-      <c r="K31" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="L31" t="s">
+        <v>18</v>
+      </c>
+      <c r="N31" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" t="s">
+        <v>16</v>
+      </c>
+      <c r="D32" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" t="s">
+        <v>17</v>
+      </c>
+      <c r="N32" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>76</v>
       </c>
-      <c r="C32" t="s">
-        <v>15</v>
-      </c>
-      <c r="D32" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" t="s">
-        <v>16</v>
-      </c>
-      <c r="M32" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>75</v>
-      </c>
       <c r="B33" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C33" t="s">
-        <v>15</v>
-      </c>
-      <c r="J33" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K33" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B34" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>79</v>
       </c>
-      <c r="C34" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>78</v>
-      </c>
       <c r="B35" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C35" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J35" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+      <c r="K35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B36" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C36" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E36" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B37" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C37" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E37" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I38" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" t="s">
-        <v>16</v>
-      </c>
-      <c r="M38" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L38" t="s">
+        <v>17</v>
+      </c>
+      <c r="N38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E39" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K39" t="s">
-        <v>16</v>
-      </c>
-      <c r="M39" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L39" t="s">
+        <v>17</v>
+      </c>
+      <c r="N39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>15</v>
-      </c>
-      <c r="J40" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="K40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E41" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F41" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I41" t="s">
-        <v>16</v>
-      </c>
-      <c r="J41" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K41" t="s">
-        <v>16</v>
-      </c>
-      <c r="M41" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+      <c r="L41" t="s">
+        <v>17</v>
+      </c>
+      <c r="N41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E42" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F42" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I42" t="s">
-        <v>16</v>
-      </c>
-      <c r="J42" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K42" t="s">
-        <v>16</v>
-      </c>
-      <c r="M42" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="L42" t="s">
+        <v>17</v>
+      </c>
+      <c r="N42" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/sof_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9194DB5CF8DC92D76EE349B7871D84ECF" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BAA33EBF-9514-4CE7-BD66-F8199C612438}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538CEA9A-3F78-479F-842C-79077A197EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="760" windowWidth="14400" windowHeight="8170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 02-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 02-10-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
@@ -653,9 +653,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N42"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -699,7 +699,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>14</v>
       </c>
@@ -722,7 +722,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>19</v>
       </c>
@@ -757,7 +757,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -795,7 +795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>24</v>
       </c>
@@ -833,7 +833,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -856,7 +856,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -870,7 +870,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -902,7 +902,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>31</v>
       </c>
@@ -943,7 +943,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>33</v>
       </c>
@@ -984,7 +984,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>35</v>
       </c>
@@ -1001,7 +1001,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1018,7 +1018,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>39</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>41</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>43</v>
       </c>
@@ -1084,7 +1084,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>45</v>
       </c>
@@ -1116,7 +1116,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>47</v>
       </c>
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>49</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1194,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>53</v>
       </c>
@@ -1235,7 +1235,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>55</v>
       </c>
@@ -1276,7 +1276,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>57</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>59</v>
       </c>
@@ -1352,7 +1352,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>59</v>
       </c>
@@ -1390,7 +1390,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>62</v>
       </c>
@@ -1428,7 +1428,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>64</v>
       </c>
@@ -1466,7 +1466,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>66</v>
       </c>
@@ -1504,7 +1504,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -1542,7 +1542,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>70</v>
       </c>
@@ -1580,7 +1580,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>72</v>
       </c>
@@ -1612,7 +1612,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>74</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>76</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>76</v>
       </c>
@@ -1669,7 +1669,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>79</v>
       </c>
@@ -1683,7 +1683,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>79</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>82</v>
       </c>
@@ -1714,7 +1714,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>84</v>
       </c>
@@ -1728,7 +1728,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>86</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>88</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>90</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>92</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>94</v>
       </c>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538CEA9A-3F78-479F-842C-79077A197EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9194DB5CF8DC92DCADEB1BFDC70D84ECB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B63303A-F8E1-4CF0-B120-E0EC4430BAC9}"/>
   <bookViews>
-    <workbookView xWindow="4680" yWindow="4680" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 07-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 07-10-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 08-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9194DB5CF8DC92DCADEB1BFDC70D84ECB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B63303A-F8E1-4CF0-B120-E0EC4430BAC9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D94B1B-D3B4-44B9-9ADF-2C004EDF4F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 08-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 08-10-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 09-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hua\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D94B1B-D3B4-44B9-9ADF-2C004EDF4F09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93D5BAD-E4B9-4A4E-B8BC-DC4BF88349A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>

--- a/html/Lægesystemer - sende_excel.XLSX
+++ b/html/Lægesystemer - sende_excel.XLSX
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Documents\GitHub\GodkendteSystemer\html\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://medcomdk-my.sharepoint.com/personal/ras_medcom_dk/Documents/Dokumenter/GitHub/GodkendteSystemer/html/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F93D5BAD-E4B9-4A4E-B8BC-DC4BF88349A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_BEA61AB9194DB5CF8DC92D685E77A07271D84ECB" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DAB2A8BF-4137-44E0-B404-767F2F320409}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-15" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1710" yWindow="1560" windowWidth="14400" windowHeight="8205" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdateret d. 09-10-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="Opdateret d. 23-10-2026" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Lægesystemer___sende">'Opdateret d. 09-10-2026'!$A$1:$N$42</definedName>
+    <definedName name="Lægesystemer___sende">'Opdateret d. 23-10-2026'!$A$1:$N$42</definedName>
   </definedNames>
   <calcPr calcId="125725"/>
 </workbook>
